--- a/Luckyday/pet/petskill_v13.xlsx
+++ b/Luckyday/pet/petskill_v13.xlsx
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>두두에게 방패 2개를 부여합니다.</t>
+          <t>두두에게 방패 1개를 부여합니다.</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="H30" s="19" t="inlineStr">
         <is>
-          <t>3턴간 저주의 가시 상태가 됩니다. 두두 피격 시 방패가 1개 자동 생성됩니다. (최대 3개)</t>
+          <t>두두에게 방패 3개를 부여합니다.</t>
         </is>
       </c>
       <c r="I30" s="19" t="inlineStr">
         <is>
-          <t>방패 소모 시 적에게 저체온 1스택을 부여하고, 두두에게 공격력 8% 증가 버프를 1턴간 걸어줍니다.</t>
+          <t>3턴간 두두 피격 시 방패를 1개 생성해줍니다.</t>
         </is>
       </c>
       <c r="J30" s="19" t="inlineStr">
